--- a/OMOP Analysis/Results/Cohort/Output_overall_healthcare_roles-OMOP.xlsx
+++ b/OMOP Analysis/Results/Cohort/Output_overall_healthcare_roles-OMOP.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,65 +375,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B2">
-        <v>327342</v>
+        <v>6651</v>
       </c>
       <c r="C2">
-        <v>37.31</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B3">
-        <v>325922</v>
+        <v>327106</v>
       </c>
       <c r="C3">
-        <v>37.15</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B4">
-        <v>85458</v>
+        <v>325922</v>
       </c>
       <c r="C4">
-        <v>9.74</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B5">
-        <v>107565</v>
+        <v>236</v>
       </c>
       <c r="C5">
-        <v>12.26</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Non-registered other</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>121461</v>
+      </c>
+      <c r="C6">
+        <v>13.84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>42557</v>
+      </c>
+      <c r="C7">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>22347</v>
+      </c>
+      <c r="C8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Social</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B10">
         <v>31006</v>
       </c>
-      <c r="C6">
+      <c r="C10">
         <v>3.53</v>
       </c>
     </row>
@@ -472,313 +524,313 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="C2">
-        <v>76318</v>
+        <v>51</v>
       </c>
       <c r="D2">
-        <v>8.699999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="C3">
-        <v>20920</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="C4">
-        <v>118097</v>
+        <v>426</v>
       </c>
       <c r="D4">
-        <v>13.46</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="C5">
-        <v>3961</v>
+        <v>5488</v>
       </c>
       <c r="D5">
-        <v>0.45</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Registered Record Administrator</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="C6">
-        <v>107810</v>
+        <v>468</v>
       </c>
       <c r="D6">
-        <v>12.29</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Student</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="C7">
-        <v>236</v>
+        <v>112</v>
       </c>
       <c r="D7">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Radiography Technologist</t>
         </is>
       </c>
       <c r="C8">
-        <v>325922</v>
+        <v>28</v>
       </c>
       <c r="D8">
-        <v>37.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>AHP</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="C9">
-        <v>11862</v>
+        <v>75</v>
       </c>
       <c r="D9">
-        <v>1.35</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Case Manager / Care Coordinator</t>
         </is>
       </c>
       <c r="C10">
-        <v>42901</v>
+        <v>76318</v>
       </c>
       <c r="D10">
-        <v>4.89</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Health Information Technician</t>
         </is>
       </c>
       <c r="C11">
-        <v>90</v>
+        <v>20920</v>
       </c>
       <c r="D11">
-        <v>0.01</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Other Technician</t>
         </is>
       </c>
       <c r="C12">
-        <v>1916</v>
+        <v>118097</v>
       </c>
       <c r="D12">
-        <v>0.22</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Physician Office Based Coding Specialist</t>
         </is>
       </c>
       <c r="C13">
-        <v>15197</v>
+        <v>3961</v>
       </c>
       <c r="D13">
-        <v>1.73</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Record Administrator</t>
         </is>
       </c>
       <c r="C14">
-        <v>3848</v>
+        <v>107810</v>
       </c>
       <c r="D14">
-        <v>0.44</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="C15">
-        <v>9644</v>
+        <v>325922</v>
       </c>
       <c r="D15">
-        <v>1.1</v>
+        <v>37.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Behavioral Health &amp; Social Service Providers, Psychologist, Clinical</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>236</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Behavioral Health &amp; Social Service Providers, Psychologist, Clinical</t>
         </is>
       </c>
       <c r="C17">
-        <v>22347</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>2.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="C18">
-        <v>51</v>
+        <v>42901</v>
       </c>
       <c r="D18">
-        <v>0.01</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -796,142 +848,142 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>6094</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="C21">
-        <v>426</v>
+        <v>6136</v>
       </c>
       <c r="D21">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="C22">
-        <v>5488</v>
+        <v>28368</v>
       </c>
       <c r="D22">
-        <v>0.63</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="C23">
-        <v>6094</v>
+        <v>141</v>
       </c>
       <c r="D23">
-        <v>0.6899999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="C24">
-        <v>6136</v>
+        <v>593</v>
       </c>
       <c r="D24">
-        <v>0.7</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Surgical Physician Assistant</t>
         </is>
       </c>
       <c r="C25">
-        <v>468</v>
+        <v>543</v>
       </c>
       <c r="D25">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="C26">
-        <v>28368</v>
+        <v>11862</v>
       </c>
       <c r="D26">
-        <v>3.23</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="C27">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="D27">
         <v>0.01</v>
@@ -940,109 +992,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="C28">
-        <v>141</v>
+        <v>1916</v>
       </c>
       <c r="D28">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Radiography Technologist</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="C29">
-        <v>28</v>
+        <v>15197</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="C30">
-        <v>75</v>
+        <v>3848</v>
       </c>
       <c r="D30">
-        <v>0.01</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="C31">
-        <v>7</v>
+        <v>9644</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Specialist</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="C32">
-        <v>593</v>
+        <v>22347</v>
       </c>
       <c r="D32">
-        <v>0.07000000000000001</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Surgical Physician Assistant</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="C33">
-        <v>543</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
